--- a/QA-Feedback-Money-App-2026.xlsx
+++ b/QA-Feedback-Money-App-2026.xlsx
@@ -20,6 +20,8 @@
     <sheet name="Tools" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Settings" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Sidebar &amp; Nav" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Beta v0.1 Features" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Scope Comparison" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Global - Site-Wide'!$A$1:$J$15</definedName>
@@ -43,7 +45,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,8 +63,38 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00228B22"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00e4e4eb"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0022c55e"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="003b82f6"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00f59e0b"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007c6ff7"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -119,6 +151,26 @@
         <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00111118"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000a2e0a"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000a1a2e"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002e2a0a"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -146,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -180,6 +232,20 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -640,9 +706,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -688,9 +754,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -736,9 +802,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -784,9 +850,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -832,9 +898,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -880,9 +946,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -908,9 +974,9 @@
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -924,9 +990,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -940,9 +1006,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -956,9 +1022,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -972,9 +1038,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -988,9 +1054,9 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -1004,9 +1070,9 @@
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -1020,9 +1086,9 @@
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -1136,9 +1202,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1184,9 +1250,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1232,9 +1298,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1276,9 +1342,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1300,9 +1366,9 @@
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -1316,9 +1382,9 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -1332,9 +1398,9 @@
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -1348,9 +1414,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -1364,9 +1430,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -1380,9 +1446,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -1396,9 +1462,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -1412,9 +1478,9 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -1528,9 +1594,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1572,9 +1638,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1616,9 +1682,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1644,9 +1710,9 @@
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
@@ -1660,9 +1726,9 @@
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -1676,9 +1742,9 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -1692,9 +1758,9 @@
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -1708,9 +1774,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -1724,9 +1790,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -1740,9 +1806,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -1756,9 +1822,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -1872,9 +1938,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1920,9 +1986,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1968,9 +2034,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -2016,9 +2082,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -2060,9 +2126,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2104,9 +2170,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -2148,9 +2214,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -2172,9 +2238,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -2188,9 +2254,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -2204,9 +2270,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -2220,9 +2286,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -2236,9 +2302,9 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -2252,9 +2318,9 @@
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -2268,9 +2334,9 @@
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -2284,9 +2350,9 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -2400,9 +2466,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -2448,9 +2514,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -2544,9 +2610,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -2592,9 +2658,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -2636,9 +2702,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -2712,9 +2778,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -2728,9 +2794,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -2744,9 +2810,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -2760,9 +2826,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -2776,9 +2842,9 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -2792,9 +2858,9 @@
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -2808,9 +2874,9 @@
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -2824,9 +2890,9 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -2836,6 +2902,794 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J16"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Glass design system</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Frosted cards, mouse glow, GlassCard</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>5 CSS background themes</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Midnight Pro, Neon Split, Solar Flare, Northern Glow, Electric Violet</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Background image editor</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>12 presets, upload, crop, focal point, scrim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>10 color themes</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>5 original + 5 grey-with-hue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Pastel + vivid chart palettes</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>COLORS (fills) + VIVID (strokes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Mouse glow effect</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Visual</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>CSS pseudo-element + JS tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Cloud sync (8 categories)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Dashboards, settings, themes, backgrounds, tool drafts</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Tier system (free/pro/premium)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>UpgradeGate, FeatureBadge, beta mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Transaction Tracker</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Pro Feature</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Full CRUD, search, filter, category breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Paycheck X-Ray (full)</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>6 charts, waterfall, pay period table, LTI</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Snapshot FAB</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Camera button on all pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Undo/redo</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Ctrl+Z, 30-state history, auto-hide after 5s</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>PWA manifest + icons</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>manifest.json, SVG icons, meta tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Error boundary</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Catches crashes, shows recovery UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Pay frequency support</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Weekly/biweekly/semimonthly/monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Share button</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Read-only links via Supabase</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Month-over-month deltas</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Latest this month vs latest last month</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Mobile month picker</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Accounts, Investments, Debt pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>NumberInput portal</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>createPortal escapes overflow:hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Scroll-to-top</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>On every route navigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Editable page titles</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>Click any title to rename</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Security audit</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Clean</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>Zero vulnerabilities found</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Accessibility audit</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>aria-labels, focus-visible, heading hierarchy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Stripe integration</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Infrastructure</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Need publishable key + price IDs</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Charts month comparison</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Side-by-side month overlay</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Notifications/reminders</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Days since last snapshot banner</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="18" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Planned phases</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>Delivered phases</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Unplanned features built</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Total features shipped</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>47+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>New files created</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Files modified</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>30+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Git commits this session</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>45+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Pages in the app</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Color themes</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Background themes</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>17 (5 CSS + 12 photo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Security vulnerabilities</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Console errors</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2940,9 +3794,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -2988,9 +3842,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -3036,9 +3890,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -3084,9 +3938,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3132,9 +3986,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -3180,9 +4034,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -3204,9 +4058,9 @@
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -3220,9 +4074,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -3236,9 +4090,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -3252,9 +4106,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -3268,9 +4122,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -3284,9 +4138,9 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -3300,9 +4154,9 @@
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -3316,9 +4170,9 @@
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -3432,9 +4286,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -3480,9 +4334,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -3528,9 +4382,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -3576,9 +4430,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3624,9 +4478,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -3672,9 +4526,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -3748,9 +4602,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -3764,9 +4618,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -3780,9 +4634,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -3796,9 +4650,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -3812,9 +4666,9 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -3828,9 +4682,9 @@
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -3844,9 +4698,9 @@
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -3860,9 +4714,9 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -3976,9 +4830,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -4024,9 +4878,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -4072,9 +4926,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -4120,9 +4974,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -4144,9 +4998,9 @@
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -4160,9 +5014,9 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -4176,9 +5030,9 @@
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -4192,9 +5046,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -4208,9 +5062,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -4224,9 +5078,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -4240,9 +5094,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -4256,9 +5110,9 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -4372,9 +5226,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -4420,9 +5274,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -4464,9 +5318,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -4488,9 +5342,9 @@
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
@@ -4504,9 +5358,9 @@
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -4520,9 +5374,9 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -4536,9 +5390,9 @@
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -4552,9 +5406,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -4568,9 +5422,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -4584,9 +5438,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -4600,9 +5454,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -4716,9 +5570,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -4764,9 +5618,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -4808,9 +5662,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -4832,9 +5686,9 @@
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
@@ -4848,9 +5702,9 @@
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -4864,9 +5718,9 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -4880,9 +5734,9 @@
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -4896,9 +5750,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -4912,9 +5766,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -4928,9 +5782,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -4944,9 +5798,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -5060,9 +5914,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -5108,9 +5962,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -5152,9 +6006,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -5180,9 +6034,9 @@
       <c r="C5" s="2" t="inlineStr"/>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
@@ -5196,9 +6050,9 @@
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
@@ -5212,9 +6066,9 @@
       <c r="C7" s="2" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
@@ -5228,9 +6082,9 @@
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -5244,9 +6098,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -5260,9 +6114,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -5276,9 +6130,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -5292,9 +6146,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -5408,9 +6262,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -5456,9 +6310,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -5504,9 +6358,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -5552,9 +6406,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -5600,9 +6454,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -5644,9 +6498,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -5672,9 +6526,9 @@
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -5688,9 +6542,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -5704,9 +6558,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -5720,9 +6574,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -5736,9 +6590,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -5752,9 +6606,9 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -5768,9 +6622,9 @@
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -5784,9 +6638,9 @@
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -5900,9 +6754,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -5948,9 +6802,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -5996,9 +6850,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -6044,9 +6898,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -6092,9 +6946,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -6140,9 +6994,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -6184,9 +7038,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -6208,9 +7062,9 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -6224,9 +7078,9 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
@@ -6240,9 +7094,9 @@
       <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -6256,9 +7110,9 @@
       <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -6272,9 +7126,9 @@
       <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -6288,9 +7142,9 @@
       <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -6304,9 +7158,9 @@
       <c r="C15" s="2" t="inlineStr"/>
       <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -6320,9 +7174,9 @@
       <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
+      <c r="F16" s="12" t="inlineStr">
+        <is>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
